--- a/tools/importer/reports/import-solutions.report.xlsx
+++ b/tools/importer/reports/import-solutions.report.xlsx
@@ -64,7 +64,7 @@
     <t>en/solutions/host-response-infection.report.json</t>
   </si>
   <si>
-    <t>["hero-left","cards-grid-features","cards-grid-video","cards-grid-video","table-grouped","columns","cards-grid-showcase","cards-grid-showcase","carousel-resources"]</t>
+    <t>["hero-left","cards-grid-features","cards-grid-video","cards-grid-video","table-grouped","columns","cards-grid-showcase","cards-grid-showcase","carousel-resources","form","form","form"]</t>
   </si>
   <si>
     <t>en/solutions/host-response-infection</t>
@@ -73,7 +73,7 @@
     <t>solutions</t>
   </si>
   <si>
-    <t>2026-10-21T09:52:06.558Z</t>
+    <t>2026-10-21T13:18:34.822Z</t>
   </si>
   <si>
     <t>Host Response Infection | Beckman Coulter</t>

--- a/tools/importer/reports/import-solutions.report.xlsx
+++ b/tools/importer/reports/import-solutions.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>_reportFile</t>
   </si>
@@ -73,13 +73,34 @@
     <t>solutions</t>
   </si>
   <si>
-    <t>2026-10-21T13:18:34.822Z</t>
+    <t>2026-10-22T07:38:20.845Z</t>
   </si>
   <si>
     <t>Host Response Infection | Beckman Coulter</t>
   </si>
   <si>
     <t>https://www.beckmancoulter.com/en/solutions/host-response-infection</t>
+  </si>
+  <si>
+    <t>en/products/dxs-service-and-supports/remote-services-and-diagnostics.report.json</t>
+  </si>
+  <si>
+    <t>["hero-split-left","cards-grid-features-purple","columns-video","content-reversed","carousel-resources","quote-banner","cards-grid-solutions"]</t>
+  </si>
+  <si>
+    <t>en/products/dxs-service-and-supports/remote-services-and-diagnostics</t>
+  </si>
+  <si>
+    <t>dxs-service-and-supports</t>
+  </si>
+  <si>
+    <t>2026-10-22T07:10:09.012Z</t>
+  </si>
+  <si>
+    <t>Remote Services and Diagnostics | Beckman Coulter</t>
+  </si>
+  <si>
+    <t>https://www.beckmancoulter.com/en/products/dxs-service-and-supports/remote-services-and-diagnostics</t>
   </si>
 </sst>
 </file>
@@ -468,15 +489,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="38" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="43" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
+    <col min="5" max="6" width="26" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -555,6 +573,32 @@
       </c>
       <c r="H3" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
